--- a/output/StructureDefinition-t-cabs-observation-beatmungsparameter.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-beatmungsparameter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T17:13:04+01:00</t>
+    <t>2025-11-21T13:42:11+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-beatmungsparameter.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-beatmungsparameter.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$130</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5234" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5275" uniqueCount="736">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T13:42:11+01:00</t>
+    <t>2025-11-25T10:29:35+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -802,10 +802,28 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:VSCat</t>
+  </si>
+  <si>
+    <t>VSCat</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
+    &lt;code value="procedure"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1141,10 +1159,6 @@
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
   </si>
   <si>
     <t>closed</t>
@@ -2610,7 +2624,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR129"/>
+  <dimension ref="A1:AR130"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.75390625" customWidth="true" bestFit="true"/>
@@ -5438,7 +5452,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>244</v>
       </c>
@@ -5451,7 +5465,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>83</v>
@@ -5515,16 +5529,14 @@
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>244</v>
@@ -5557,10 +5569,10 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5568,14 +5580,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>255</v>
+        <v>84</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5591,22 +5605,22 @@
         <v>84</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>245</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5616,7 +5630,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>84</v>
+        <v>257</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5631,11 +5645,13 @@
         <v>84</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5653,13 +5669,13 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>84</v>
@@ -5674,62 +5690,66 @@
         <v>84</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>261</v>
+        <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>262</v>
+        <v>84</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>263</v>
+        <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>266</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>84</v>
+        <v>259</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>109</v>
+        <v>245</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
       </c>
@@ -5753,13 +5773,11 @@
         <v>84</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>84</v>
+        <v>264</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5777,10 +5795,10 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>112</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>95</v>
@@ -5789,7 +5807,7 @@
         <v>84</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>84</v>
@@ -5798,41 +5816,41 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>84</v>
+        <v>266</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>113</v>
+        <v>268</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>84</v>
+        <v>269</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>84</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>84</v>
@@ -5844,17 +5862,15 @@
         <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5891,31 +5907,31 @@
         <v>84</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>84</v>
@@ -5942,16 +5958,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5961,29 +5977,27 @@
         <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>270</v>
+        <v>117</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>271</v>
+        <v>118</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>84</v>
       </c>
@@ -6019,19 +6033,19 @@
         <v>84</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>274</v>
+        <v>123</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6043,7 +6057,7 @@
         <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>84</v>
@@ -6058,10 +6072,10 @@
         <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>275</v>
+        <v>84</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>276</v>
+        <v>113</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -6070,12 +6084,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6086,28 +6100,32 @@
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>110</v>
+        <v>274</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
       </c>
@@ -6155,19 +6173,19 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>112</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>84</v>
@@ -6182,10 +6200,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>113</v>
+        <v>280</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -6196,21 +6214,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>84</v>
@@ -6222,17 +6240,15 @@
         <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -6269,31 +6285,31 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>84</v>
@@ -6322,21 +6338,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>84</v>
@@ -6345,23 +6361,21 @@
         <v>84</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>280</v>
+        <v>117</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>281</v>
+        <v>118</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
@@ -6397,37 +6411,37 @@
         <v>84</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>284</v>
+        <v>123</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>285</v>
+        <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>84</v>
@@ -6436,10 +6450,10 @@
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>286</v>
+        <v>84</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>287</v>
+        <v>113</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
@@ -6450,10 +6464,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6476,18 +6490,20 @@
         <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -6535,7 +6551,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6553,7 +6569,7 @@
         <v>84</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>84</v>
@@ -6562,10 +6578,10 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6576,10 +6592,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6602,18 +6618,18 @@
         <v>96</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>84</v>
       </c>
@@ -6661,7 +6677,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6676,10 +6692,10 @@
         <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>84</v>
@@ -6688,10 +6704,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6702,10 +6718,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6728,17 +6744,17 @@
         <v>96</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6787,7 +6803,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6802,10 +6818,10 @@
         <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>305</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>84</v>
+        <v>306</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>84</v>
@@ -6814,10 +6830,10 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6828,10 +6844,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6854,19 +6870,17 @@
         <v>96</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>313</v>
+        <v>109</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6915,7 +6929,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6942,10 +6956,10 @@
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6956,10 +6970,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6982,19 +6996,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>109</v>
+        <v>317</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -7043,7 +7057,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7070,10 +7084,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -7082,12 +7096,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7095,13 +7109,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
@@ -7110,19 +7124,19 @@
         <v>96</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>330</v>
+        <v>109</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -7171,7 +7185,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7192,30 +7206,30 @@
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>335</v>
+        <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>338</v>
+        <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7223,13 +7237,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>84</v>
@@ -7238,18 +7252,20 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
       </c>
@@ -7297,13 +7313,13 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>84</v>
@@ -7318,19 +7334,19 @@
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>84</v>
+        <v>339</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>263</v>
+        <v>340</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -7338,21 +7354,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>346</v>
+        <v>84</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>84</v>
@@ -7364,20 +7380,18 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L38" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>351</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
@@ -7425,13 +7439,13 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>84</v>
@@ -7446,19 +7460,19 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>352</v>
+        <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>353</v>
+        <v>267</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7466,24 +7480,24 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>84</v>
@@ -7492,19 +7506,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7541,17 +7555,19 @@
         <v>84</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AC39" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>364</v>
+        <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7572,19 +7588,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7592,26 +7608,24 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>84</v>
@@ -7620,19 +7634,19 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7669,19 +7683,17 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>84</v>
+        <v>367</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7696,25 +7708,25 @@
         <v>107</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>372</v>
+        <v>84</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7722,16 +7734,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C41" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="B41" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>374</v>
-      </c>
       <c r="D41" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7750,19 +7762,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7811,7 +7823,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7826,25 +7838,25 @@
         <v>107</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7855,11 +7867,13 @@
         <v>376</v>
       </c>
       <c r="B42" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C42" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>84</v>
+        <v>361</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7875,19 +7889,23 @@
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>109</v>
+        <v>378</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>110</v>
+        <v>363</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7935,7 +7953,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>112</v>
+        <v>360</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7947,7 +7965,7 @@
         <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>84</v>
@@ -7956,19 +7974,19 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>84</v>
+        <v>368</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>113</v>
+        <v>370</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>84</v>
+        <v>371</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7976,21 +7994,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>84</v>
@@ -8002,17 +8020,15 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -8049,31 +8065,31 @@
         <v>84</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -8102,21 +8118,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>84</v>
@@ -8125,19 +8141,19 @@
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>371</v>
+        <v>116</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>382</v>
+        <v>117</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>383</v>
+        <v>118</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>384</v>
+        <v>119</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -8175,37 +8191,37 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>385</v>
+        <v>123</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>388</v>
+        <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>84</v>
@@ -8214,10 +8230,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>390</v>
+        <v>113</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8228,10 +8244,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8254,24 +8270,22 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q45" t="s" s="2">
-        <v>396</v>
-      </c>
+      <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
         <v>84</v>
       </c>
@@ -8315,7 +8329,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8324,16 +8338,16 @@
         <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>84</v>
@@ -8342,10 +8356,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8356,16 +8370,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>357</v>
+        <v>84</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -8384,24 +8396,24 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>131</v>
+        <v>374</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q46" s="2"/>
+      <c r="Q46" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="R46" t="s" s="2">
         <v>84</v>
       </c>
@@ -8445,7 +8457,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>356</v>
+        <v>400</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8454,31 +8466,31 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>84</v>
+        <v>389</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="AQ46" t="s" s="2">
-        <v>368</v>
+        <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>84</v>
@@ -8489,11 +8501,13 @@
         <v>405</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="D47" t="s" s="2">
-        <v>84</v>
+        <v>361</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8515,15 +8529,17 @@
         <v>131</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>406</v>
+        <v>363</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>407</v>
+        <v>364</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -8571,7 +8587,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>405</v>
+        <v>360</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8589,22 +8605,22 @@
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>84</v>
+        <v>407</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>84</v>
+        <v>368</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>409</v>
+        <v>369</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -8612,10 +8628,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8626,7 +8642,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>84</v>
@@ -8638,18 +8654,18 @@
         <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>413</v>
+        <v>131</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8697,13 +8713,13 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
@@ -8718,19 +8734,19 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>417</v>
+        <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -8738,10 +8754,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8752,10 +8768,10 @@
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>84</v>
@@ -8764,19 +8780,17 @@
         <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8813,26 +8827,28 @@
         <v>84</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AC49" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>364</v>
+        <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>427</v>
+        <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>107</v>
@@ -8844,34 +8860,32 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>428</v>
+        <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>84</v>
+        <v>423</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8883,7 +8897,7 @@
         <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>84</v>
@@ -8892,19 +8906,19 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8941,19 +8955,17 @@
         <v>84</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>84</v>
+        <v>367</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8962,7 +8974,7 @@
         <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
@@ -8977,29 +8989,31 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="B51" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>84</v>
       </c>
@@ -9017,19 +9031,23 @@
         <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>109</v>
+        <v>437</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>110</v>
+        <v>426</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -9077,7 +9095,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>112</v>
+        <v>424</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9086,10 +9104,10 @@
         <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>84</v>
+        <v>438</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -9101,38 +9119,38 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>84</v>
+        <v>431</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>84</v>
+        <v>432</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>113</v>
+        <v>433</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>84</v>
+        <v>434</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
@@ -9144,17 +9162,15 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9191,31 +9207,31 @@
         <v>84</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -9244,21 +9260,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>84</v>
@@ -9267,23 +9283,21 @@
         <v>84</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>442</v>
+        <v>116</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>443</v>
+        <v>117</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>444</v>
+        <v>118</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -9319,37 +9333,37 @@
         <v>84</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>447</v>
+        <v>123</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>448</v>
+        <v>84</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>84</v>
@@ -9358,10 +9372,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>451</v>
+        <v>113</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9372,10 +9386,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9383,7 +9397,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>95</v>
@@ -9392,30 +9406,30 @@
         <v>84</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>172</v>
+        <v>445</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q54" t="s" s="2">
-        <v>457</v>
-      </c>
+      <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
         <v>84</v>
       </c>
@@ -9435,13 +9449,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>236</v>
+        <v>84</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>458</v>
+        <v>84</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>459</v>
+        <v>84</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9459,7 +9473,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9474,10 +9488,10 @@
         <v>107</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>84</v>
+        <v>452</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>84</v>
@@ -9486,10 +9500,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9500,10 +9514,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9520,28 +9534,30 @@
         <v>84</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q55" s="2"/>
+      <c r="Q55" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="R55" t="s" s="2">
         <v>84</v>
       </c>
@@ -9561,13 +9577,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9585,7 +9601,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9612,10 +9628,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9626,10 +9642,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9652,24 +9668,24 @@
         <v>96</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>84</v>
@@ -9711,7 +9727,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9720,7 +9736,7 @@
         <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>478</v>
+        <v>84</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>107</v>
@@ -9738,10 +9754,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9752,10 +9768,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9778,26 +9794,24 @@
         <v>96</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>84</v>
+        <v>479</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>84</v>
@@ -9839,7 +9853,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9848,13 +9862,13 @@
         <v>95</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>84</v>
+        <v>481</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>487</v>
+        <v>84</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>84</v>
@@ -9866,10 +9880,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9880,14 +9894,12 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9908,19 +9920,19 @@
         <v>96</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>491</v>
+        <v>172</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>423</v>
+        <v>485</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>425</v>
+        <v>487</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>426</v>
+        <v>488</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9969,7 +9981,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>421</v>
+        <v>489</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9978,13 +9990,13 @@
         <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>435</v>
+        <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>84</v>
+        <v>490</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>84</v>
@@ -9993,19 +10005,19 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>428</v>
+        <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>429</v>
+        <v>472</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>430</v>
+        <v>491</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -10013,9 +10025,11 @@
         <v>492</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>84</v>
       </c>
@@ -10033,19 +10047,23 @@
         <v>84</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>109</v>
+        <v>494</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>110</v>
+        <v>426</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
       </c>
@@ -10093,7 +10111,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>112</v>
+        <v>424</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10102,10 +10120,10 @@
         <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>84</v>
+        <v>438</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -10117,38 +10135,38 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>84</v>
+        <v>431</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>84</v>
+        <v>432</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>113</v>
+        <v>433</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>84</v>
+        <v>434</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>84</v>
@@ -10160,17 +10178,15 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -10207,31 +10223,31 @@
         <v>84</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -10260,21 +10276,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>495</v>
+        <v>442</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>84</v>
@@ -10283,18 +10299,20 @@
         <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>434</v>
+        <v>116</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>496</v>
+        <v>117</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10331,31 +10349,31 @@
         <v>84</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>498</v>
+        <v>123</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>84</v>
@@ -10373,7 +10391,7 @@
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>499</v>
+        <v>113</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10384,10 +10402,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10407,16 +10425,16 @@
         <v>84</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>109</v>
+        <v>437</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>110</v>
+        <v>499</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>111</v>
+        <v>500</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10467,7 +10485,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>112</v>
+        <v>501</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10479,7 +10497,7 @@
         <v>84</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>84</v>
@@ -10497,7 +10515,7 @@
         <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>113</v>
+        <v>502</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10508,21 +10526,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>84</v>
@@ -10534,17 +10552,15 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10581,31 +10597,31 @@
         <v>84</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>84</v>
@@ -10634,21 +10650,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>84</v>
@@ -10657,23 +10673,21 @@
         <v>84</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>442</v>
+        <v>116</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>443</v>
+        <v>117</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>444</v>
+        <v>118</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>84</v>
       </c>
@@ -10709,31 +10723,31 @@
         <v>84</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>447</v>
+        <v>123</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>84</v>
@@ -10748,10 +10762,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>451</v>
+        <v>113</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10762,10 +10776,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10773,7 +10787,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>95</v>
@@ -10782,30 +10796,30 @@
         <v>84</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>172</v>
+        <v>445</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q65" t="s" s="2">
-        <v>457</v>
-      </c>
+      <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10825,13 +10839,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>236</v>
+        <v>84</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>458</v>
+        <v>84</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>459</v>
+        <v>84</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10849,7 +10863,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10876,10 +10890,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10890,10 +10904,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10910,28 +10924,30 @@
         <v>84</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q66" s="2"/>
+      <c r="Q66" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="R66" t="s" s="2">
         <v>84</v>
       </c>
@@ -10951,13 +10967,13 @@
         <v>84</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>84</v>
@@ -10975,7 +10991,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11002,10 +11018,10 @@
         <v>84</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11016,10 +11032,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11042,24 +11058,24 @@
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>84</v>
@@ -11101,7 +11117,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11110,7 +11126,7 @@
         <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>478</v>
+        <v>84</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>107</v>
@@ -11128,10 +11144,10 @@
         <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -11142,10 +11158,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11168,26 +11184,24 @@
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>84</v>
+        <v>479</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>84</v>
@@ -11229,7 +11243,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11238,7 +11252,7 @@
         <v>95</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>84</v>
+        <v>481</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>107</v>
@@ -11256,10 +11270,10 @@
         <v>84</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11270,10 +11284,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11296,16 +11310,20 @@
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>434</v>
+        <v>172</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>516</v>
+        <v>485</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
       </c>
@@ -11353,7 +11371,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11380,10 +11398,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>84</v>
+        <v>472</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>519</v>
+        <v>491</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11394,10 +11412,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11417,16 +11435,16 @@
         <v>84</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>109</v>
+        <v>437</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>110</v>
+        <v>519</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>111</v>
+        <v>520</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11477,7 +11495,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>112</v>
+        <v>521</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11489,7 +11507,7 @@
         <v>84</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>84</v>
@@ -11507,7 +11525,7 @@
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>113</v>
+        <v>522</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11518,21 +11536,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>84</v>
@@ -11544,17 +11562,15 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11591,31 +11607,31 @@
         <v>84</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>84</v>
@@ -11644,21 +11660,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>84</v>
@@ -11667,23 +11683,21 @@
         <v>84</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>442</v>
+        <v>116</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>443</v>
+        <v>117</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>444</v>
+        <v>118</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>84</v>
       </c>
@@ -11719,31 +11733,31 @@
         <v>84</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>447</v>
+        <v>123</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>84</v>
@@ -11758,10 +11772,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>451</v>
+        <v>113</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11772,10 +11786,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11783,7 +11797,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>95</v>
@@ -11792,30 +11806,30 @@
         <v>84</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>172</v>
+        <v>445</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O73" t="s" s="2">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q73" t="s" s="2">
-        <v>457</v>
-      </c>
+      <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
         <v>84</v>
       </c>
@@ -11835,13 +11849,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>236</v>
+        <v>84</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>458</v>
+        <v>84</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>459</v>
+        <v>84</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -11859,7 +11873,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11886,10 +11900,10 @@
         <v>84</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11900,10 +11914,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11920,28 +11934,30 @@
         <v>84</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q74" s="2"/>
+      <c r="Q74" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="R74" t="s" s="2">
         <v>84</v>
       </c>
@@ -11961,13 +11977,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -11985,7 +12001,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12012,10 +12028,10 @@
         <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12026,10 +12042,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12052,24 +12068,24 @@
         <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>84</v>
@@ -12111,7 +12127,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12120,7 +12136,7 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>478</v>
+        <v>84</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
@@ -12138,10 +12154,10 @@
         <v>84</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -12152,10 +12168,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12178,26 +12194,24 @@
         <v>96</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>84</v>
+        <v>479</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>84</v>
@@ -12239,7 +12253,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12248,7 +12262,7 @@
         <v>95</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>84</v>
+        <v>481</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>107</v>
@@ -12266,10 +12280,10 @@
         <v>84</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12278,12 +12292,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12297,28 +12311,28 @@
         <v>95</v>
       </c>
       <c r="H77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J77" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K77" t="s" s="2">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>535</v>
+        <v>485</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>536</v>
+        <v>486</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>537</v>
+        <v>487</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>538</v>
+        <v>488</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12343,13 +12357,13 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>539</v>
+        <v>84</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>540</v>
+        <v>84</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -12367,7 +12381,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>534</v>
+        <v>489</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12376,13 +12390,13 @@
         <v>95</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>541</v>
+        <v>84</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>84</v>
@@ -12394,10 +12408,10 @@
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>195</v>
+        <v>472</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>542</v>
+        <v>491</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12408,21 +12422,21 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>544</v>
+        <v>84</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>96</v>
@@ -12437,16 +12451,16 @@
         <v>245</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12473,9 +12487,11 @@
       <c r="X78" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y78" s="2"/>
+      <c r="Y78" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="Z78" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12493,16 +12509,16 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>84</v>
+        <v>544</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>107</v>
@@ -12511,37 +12527,37 @@
         <v>157</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>550</v>
+        <v>84</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>551</v>
+        <v>84</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>552</v>
+        <v>195</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>554</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>84</v>
+        <v>547</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -12551,7 +12567,7 @@
         <v>83</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>84</v>
@@ -12560,19 +12576,19 @@
         <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>556</v>
+        <v>245</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12597,13 +12613,11 @@
         <v>84</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>84</v>
+        <v>552</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12621,7 +12635,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12636,36 +12650,36 @@
         <v>107</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>84</v>
+        <v>553</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>84</v>
+        <v>554</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>84</v>
+        <v>557</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12676,10 +12690,10 @@
         <v>82</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>84</v>
@@ -12688,18 +12702,20 @@
         <v>84</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>245</v>
+        <v>559</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>562</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
       </c>
@@ -12723,13 +12739,13 @@
         <v>84</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>567</v>
+        <v>84</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>568</v>
+        <v>84</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>84</v>
@@ -12747,13 +12763,13 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>84</v>
@@ -12771,27 +12787,27 @@
         <v>84</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>569</v>
+        <v>84</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>572</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12805,7 +12821,7 @@
         <v>95</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>84</v>
@@ -12814,15 +12830,17 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>109</v>
+        <v>245</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>110</v>
+        <v>567</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>84</v>
@@ -12847,13 +12865,13 @@
         <v>84</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>84</v>
+        <v>570</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -12871,7 +12889,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>112</v>
+        <v>566</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12883,7 +12901,7 @@
         <v>84</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>84</v>
@@ -12895,38 +12913,38 @@
         <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>84</v>
+        <v>573</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>113</v>
+        <v>574</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR81" t="s" s="2">
-        <v>84</v>
+        <v>575</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>84</v>
@@ -12938,17 +12956,15 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -12985,31 +13001,31 @@
         <v>84</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>84</v>
@@ -13038,14 +13054,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -13061,23 +13077,21 @@
         <v>84</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>270</v>
+        <v>117</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>271</v>
+        <v>118</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>84</v>
       </c>
@@ -13113,19 +13127,19 @@
         <v>84</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>274</v>
+        <v>123</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13137,7 +13151,7 @@
         <v>84</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>84</v>
@@ -13152,10 +13166,10 @@
         <v>84</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>275</v>
+        <v>84</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>276</v>
+        <v>113</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13166,10 +13180,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13180,7 +13194,7 @@
         <v>82</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>84</v>
@@ -13189,19 +13203,23 @@
         <v>84</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>110</v>
+        <v>274</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
       </c>
@@ -13249,19 +13267,19 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>112</v>
+        <v>278</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>84</v>
@@ -13276,10 +13294,10 @@
         <v>84</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>113</v>
+        <v>280</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13290,21 +13308,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>84</v>
@@ -13316,17 +13334,15 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13363,31 +13379,31 @@
         <v>84</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>84</v>
@@ -13416,21 +13432,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>84</v>
@@ -13439,23 +13455,21 @@
         <v>84</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>280</v>
+        <v>117</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>281</v>
+        <v>118</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>84</v>
       </c>
@@ -13491,37 +13505,37 @@
         <v>84</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>284</v>
+        <v>123</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>579</v>
+        <v>84</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>84</v>
@@ -13530,10 +13544,10 @@
         <v>84</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>286</v>
+        <v>84</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>287</v>
+        <v>113</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13544,10 +13558,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13570,18 +13584,20 @@
         <v>96</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
       </c>
@@ -13629,7 +13645,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13647,7 +13663,7 @@
         <v>84</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>84</v>
@@ -13656,10 +13672,10 @@
         <v>84</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13670,10 +13686,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13696,18 +13712,18 @@
         <v>96</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>84</v>
       </c>
@@ -13755,7 +13771,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13773,7 +13789,7 @@
         <v>84</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>84</v>
@@ -13782,10 +13798,10 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13796,10 +13812,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13822,17 +13838,17 @@
         <v>96</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -13881,7 +13897,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13899,7 +13915,7 @@
         <v>84</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>84</v>
+        <v>586</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>84</v>
@@ -13908,10 +13924,10 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -13922,10 +13938,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13948,19 +13964,17 @@
         <v>96</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>313</v>
+        <v>109</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -14009,7 +14023,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14036,10 +14050,10 @@
         <v>84</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14050,10 +14064,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14076,19 +14090,19 @@
         <v>96</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>109</v>
+        <v>317</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -14137,7 +14151,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14164,10 +14178,10 @@
         <v>84</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14178,10 +14192,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14201,22 +14215,22 @@
         <v>84</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>588</v>
+        <v>326</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>589</v>
+        <v>327</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>590</v>
+        <v>328</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>591</v>
+        <v>329</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14241,13 +14255,13 @@
         <v>84</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>592</v>
+        <v>84</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>593</v>
+        <v>84</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>84</v>
@@ -14265,7 +14279,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>587</v>
+        <v>330</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14292,10 +14306,10 @@
         <v>84</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>594</v>
+        <v>331</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>595</v>
+        <v>332</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14306,10 +14320,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14332,18 +14346,20 @@
         <v>84</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>597</v>
+        <v>245</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>594</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
       </c>
@@ -14367,13 +14383,13 @@
         <v>84</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>84</v>
+        <v>595</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>84</v>
+        <v>596</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>84</v>
@@ -14391,7 +14407,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14415,27 +14431,27 @@
         <v>84</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>601</v>
+        <v>84</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>604</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14443,13 +14459,13 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>84</v>
@@ -14458,16 +14474,16 @@
         <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14517,7 +14533,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14541,27 +14557,27 @@
         <v>84</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14569,10 +14585,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>96</v>
@@ -14584,20 +14600,18 @@
         <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>619</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>84</v>
       </c>
@@ -14645,51 +14659,51 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AO95" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="AG95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>621</v>
-      </c>
       <c r="AP95" t="s" s="2">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>84</v>
+        <v>616</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14700,10 +14714,10 @@
         <v>82</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>84</v>
@@ -14712,16 +14726,20 @@
         <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>109</v>
+        <v>618</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>110</v>
+        <v>619</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>620</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>622</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
       </c>
@@ -14769,19 +14787,19 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>112</v>
+        <v>617</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>84</v>
+        <v>623</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>84</v>
@@ -14796,10 +14814,10 @@
         <v>84</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>84</v>
+        <v>624</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>113</v>
+        <v>625</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
@@ -14810,21 +14828,21 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>84</v>
@@ -14836,17 +14854,15 @@
         <v>84</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -14895,19 +14911,19 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>84</v>
@@ -14936,14 +14952,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>626</v>
+        <v>115</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14956,26 +14972,24 @@
         <v>84</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K98" t="s" s="2">
         <v>116</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>627</v>
+        <v>117</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>628</v>
+        <v>118</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="O98" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>84</v>
       </c>
@@ -15023,7 +15037,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>629</v>
+        <v>123</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15053,7 +15067,7 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>195</v>
+        <v>113</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
@@ -15062,44 +15076,48 @@
         <v>84</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>84</v>
+        <v>629</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I99" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I99" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="J99" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="L99" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+      <c r="N99" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
       </c>
@@ -15147,25 +15165,25 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>634</v>
+        <v>84</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>635</v>
+        <v>84</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>636</v>
+        <v>84</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>84</v>
@@ -15174,10 +15192,10 @@
         <v>84</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>637</v>
+        <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>638</v>
+        <v>195</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -15186,12 +15204,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15205,7 +15223,7 @@
         <v>95</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>84</v>
@@ -15214,13 +15232,13 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>109</v>
+        <v>634</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>110</v>
+        <v>635</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>111</v>
+        <v>636</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15271,7 +15289,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>112</v>
+        <v>633</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15280,16 +15298,16 @@
         <v>95</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>84</v>
+        <v>637</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>84</v>
+        <v>638</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>84</v>
+        <v>639</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>84</v>
@@ -15298,10 +15316,10 @@
         <v>84</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>84</v>
+        <v>640</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>113</v>
+        <v>641</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15312,21 +15330,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>84</v>
@@ -15338,17 +15356,15 @@
         <v>84</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15385,31 +15401,31 @@
         <v>84</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>84</v>
@@ -15436,48 +15452,46 @@
         <v>84</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>442</v>
+        <v>116</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>443</v>
+        <v>117</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>444</v>
+        <v>118</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>84</v>
       </c>
@@ -15513,31 +15527,31 @@
         <v>84</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>447</v>
+        <v>123</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>84</v>
@@ -15552,10 +15566,10 @@
         <v>84</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>451</v>
+        <v>113</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
@@ -15564,12 +15578,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15577,39 +15591,39 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J103" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>172</v>
+        <v>445</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O103" t="s" s="2">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q103" t="s" s="2">
-        <v>457</v>
-      </c>
+      <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
         <v>84</v>
       </c>
@@ -15629,13 +15643,13 @@
         <v>84</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>236</v>
+        <v>84</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>458</v>
+        <v>84</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>459</v>
+        <v>84</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>84</v>
@@ -15653,7 +15667,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15680,10 +15694,10 @@
         <v>84</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
@@ -15692,12 +15706,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15708,34 +15722,36 @@
         <v>82</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I104" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="J104" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>466</v>
+        <v>646</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q104" s="2"/>
+      <c r="Q104" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="R104" t="s" s="2">
         <v>84</v>
       </c>
@@ -15755,13 +15771,13 @@
         <v>84</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>84</v>
@@ -15779,7 +15795,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15806,10 +15822,10 @@
         <v>84</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
@@ -15818,12 +15834,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15837,7 +15853,7 @@
         <v>95</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>84</v>
@@ -15846,17 +15862,17 @@
         <v>96</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>84</v>
@@ -15866,7 +15882,7 @@
         <v>84</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>84</v>
@@ -15905,7 +15921,7 @@
         <v>84</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15914,7 +15930,7 @@
         <v>95</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>478</v>
+        <v>84</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>107</v>
@@ -15932,10 +15948,10 @@
         <v>84</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>84</v>
@@ -15944,12 +15960,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15957,13 +15973,13 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>84</v>
@@ -15972,19 +15988,17 @@
         <v>96</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>84</v>
@@ -15994,7 +16008,7 @@
         <v>84</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>84</v>
+        <v>479</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>84</v>
@@ -16033,7 +16047,7 @@
         <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>82</v>
@@ -16042,7 +16056,7 @@
         <v>95</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>84</v>
+        <v>481</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>107</v>
@@ -16060,10 +16074,10 @@
         <v>84</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>84</v>
@@ -16074,10 +16088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16085,7 +16099,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>95</v>
@@ -16097,19 +16111,23 @@
         <v>84</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>631</v>
+        <v>172</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>648</v>
+        <v>485</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>84</v>
       </c>
@@ -16157,7 +16175,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>647</v>
+        <v>489</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16166,42 +16184,42 @@
         <v>95</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>634</v>
+        <v>84</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AQ107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR107" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="AL107" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AQ107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR107" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>653</v>
-      </c>
       <c r="B108" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16215,7 +16233,7 @@
         <v>95</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>84</v>
@@ -16224,13 +16242,13 @@
         <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>109</v>
+        <v>634</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>110</v>
+        <v>651</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>111</v>
+        <v>652</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -16281,7 +16299,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>112</v>
+        <v>650</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16290,16 +16308,16 @@
         <v>95</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>84</v>
+        <v>637</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>84</v>
+        <v>653</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>84</v>
+        <v>654</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>84</v>
@@ -16308,10 +16326,10 @@
         <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>84</v>
+        <v>640</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>113</v>
+        <v>655</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -16322,21 +16340,21 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>84</v>
@@ -16348,17 +16366,15 @@
         <v>84</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>84</v>
@@ -16395,31 +16411,31 @@
         <v>84</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>84</v>
@@ -16446,48 +16462,46 @@
         <v>84</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>442</v>
+        <v>116</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>443</v>
+        <v>117</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>444</v>
+        <v>118</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>84</v>
       </c>
@@ -16523,31 +16537,31 @@
         <v>84</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>447</v>
+        <v>123</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>84</v>
@@ -16562,10 +16576,10 @@
         <v>84</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>451</v>
+        <v>113</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
@@ -16574,12 +16588,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16587,39 +16601,39 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J111" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>172</v>
+        <v>445</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O111" t="s" s="2">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q111" t="s" s="2">
-        <v>457</v>
-      </c>
+      <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
         <v>84</v>
       </c>
@@ -16639,13 +16653,13 @@
         <v>84</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>236</v>
+        <v>84</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>458</v>
+        <v>84</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>459</v>
+        <v>84</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>84</v>
@@ -16663,7 +16677,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16690,10 +16704,10 @@
         <v>84</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -16702,12 +16716,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16718,34 +16732,36 @@
         <v>82</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I112" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="J112" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>466</v>
+        <v>646</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q112" s="2"/>
+      <c r="Q112" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="R112" t="s" s="2">
         <v>84</v>
       </c>
@@ -16765,13 +16781,13 @@
         <v>84</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>84</v>
@@ -16789,7 +16805,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -16816,10 +16832,10 @@
         <v>84</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -16828,12 +16844,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16847,7 +16863,7 @@
         <v>95</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>84</v>
@@ -16856,17 +16872,17 @@
         <v>96</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>84</v>
@@ -16876,7 +16892,7 @@
         <v>84</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>84</v>
@@ -16915,7 +16931,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -16924,7 +16940,7 @@
         <v>95</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>478</v>
+        <v>84</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>107</v>
@@ -16942,10 +16958,10 @@
         <v>84</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
@@ -16954,12 +16970,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16967,13 +16983,13 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>84</v>
@@ -16982,19 +16998,17 @@
         <v>96</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>84</v>
@@ -17004,7 +17018,7 @@
         <v>84</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>84</v>
+        <v>479</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>84</v>
@@ -17043,7 +17057,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17052,7 +17066,7 @@
         <v>95</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>84</v>
+        <v>481</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>107</v>
@@ -17070,10 +17084,10 @@
         <v>84</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
@@ -17082,12 +17096,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17095,34 +17109,34 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>661</v>
+        <v>485</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>662</v>
+        <v>486</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>663</v>
+        <v>487</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>664</v>
+        <v>488</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
@@ -17132,7 +17146,7 @@
         <v>84</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>665</v>
+        <v>84</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>84</v>
@@ -17147,13 +17161,13 @@
         <v>84</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>666</v>
+        <v>84</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>667</v>
+        <v>84</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>84</v>
@@ -17171,7 +17185,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>660</v>
+        <v>489</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17195,13 +17209,13 @@
         <v>84</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>668</v>
+        <v>84</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>669</v>
+        <v>472</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>553</v>
+        <v>491</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
@@ -17212,10 +17226,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17226,7 +17240,7 @@
         <v>82</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>84</v>
@@ -17241,16 +17255,16 @@
         <v>245</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
@@ -17260,7 +17274,7 @@
         <v>84</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>84</v>
+        <v>668</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>84</v>
@@ -17275,13 +17289,13 @@
         <v>84</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>84</v>
@@ -17299,13 +17313,13 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>84</v>
@@ -17323,13 +17337,13 @@
         <v>84</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
@@ -17340,10 +17354,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17354,7 +17368,7 @@
         <v>82</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>84</v>
@@ -17366,17 +17380,19 @@
         <v>84</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>678</v>
+        <v>245</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>675</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>676</v>
+      </c>
       <c r="O117" t="s" s="2">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17401,13 +17417,13 @@
         <v>84</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>84</v>
+        <v>678</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>84</v>
+        <v>679</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>84</v>
@@ -17425,13 +17441,13 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>84</v>
@@ -17449,13 +17465,13 @@
         <v>84</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>84</v>
+        <v>671</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>84</v>
+        <v>672</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>682</v>
+        <v>556</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
@@ -17466,10 +17482,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17492,16 +17508,18 @@
         <v>84</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>109</v>
+        <v>681</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="M118" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>84</v>
       </c>
@@ -17549,7 +17567,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17576,10 +17594,10 @@
         <v>84</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>637</v>
+        <v>84</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
@@ -17590,10 +17608,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17604,7 +17622,7 @@
         <v>82</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>84</v>
@@ -17613,20 +17631,18 @@
         <v>84</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="L119" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>691</v>
-      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>84</v>
@@ -17675,13 +17691,13 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>84</v>
@@ -17702,10 +17718,10 @@
         <v>84</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>692</v>
+        <v>640</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
@@ -17716,10 +17732,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17742,16 +17758,16 @@
         <v>96</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17801,7 +17817,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
@@ -17828,10 +17844,10 @@
         <v>84</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="AQ120" t="s" s="2">
         <v>84</v>
@@ -17842,10 +17858,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17868,20 +17884,18 @@
         <v>96</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>615</v>
+        <v>698</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="N121" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="M121" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>704</v>
-      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>84</v>
       </c>
@@ -17929,7 +17943,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -17956,10 +17970,10 @@
         <v>84</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
@@ -17970,10 +17984,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17984,7 +17998,7 @@
         <v>82</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>84</v>
@@ -17993,19 +18007,23 @@
         <v>84</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>109</v>
+        <v>618</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>110</v>
+        <v>704</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
+        <v>705</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>707</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
       </c>
@@ -18053,19 +18071,19 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>112</v>
+        <v>703</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>84</v>
@@ -18080,10 +18098,10 @@
         <v>84</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>84</v>
+        <v>708</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>113</v>
+        <v>709</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18094,21 +18112,21 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>84</v>
@@ -18120,17 +18138,15 @@
         <v>84</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>84</v>
@@ -18179,19 +18195,19 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>84</v>
@@ -18220,14 +18236,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>626</v>
+        <v>115</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -18240,26 +18256,24 @@
         <v>84</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K124" t="s" s="2">
         <v>116</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>627</v>
+        <v>117</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>628</v>
+        <v>118</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="O124" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>84</v>
       </c>
@@ -18307,7 +18321,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>629</v>
+        <v>123</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18337,7 +18351,7 @@
         <v>84</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>195</v>
+        <v>113</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>84</v>
@@ -18348,45 +18362,45 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>84</v>
+        <v>629</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J125" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>245</v>
+        <v>116</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>711</v>
+        <v>630</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>712</v>
+        <v>631</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>713</v>
+        <v>119</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>259</v>
+        <v>202</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
@@ -18411,13 +18425,13 @@
         <v>84</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>714</v>
+        <v>84</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>715</v>
+        <v>84</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>84</v>
@@ -18435,19 +18449,19 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>710</v>
+        <v>632</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>84</v>
@@ -18459,16 +18473,16 @@
         <v>84</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>716</v>
+        <v>84</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>263</v>
+        <v>84</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>265</v>
+        <v>84</v>
       </c>
       <c r="AR125" t="s" s="2">
         <v>84</v>
@@ -18476,10 +18490,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18487,7 +18501,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>95</v>
@@ -18502,19 +18516,19 @@
         <v>96</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>718</v>
+        <v>245</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>424</v>
+        <v>715</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>426</v>
+        <v>263</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -18539,13 +18553,13 @@
         <v>84</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>84</v>
+        <v>717</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>84</v>
+        <v>718</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>84</v>
@@ -18563,10 +18577,10 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>95</v>
@@ -18587,27 +18601,27 @@
         <v>84</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>429</v>
+        <v>267</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>430</v>
+        <v>268</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>84</v>
+        <v>269</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18627,22 +18641,22 @@
         <v>84</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>245</v>
+        <v>721</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N127" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="M127" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>725</v>
-      </c>
       <c r="O127" t="s" s="2">
-        <v>538</v>
+        <v>429</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>84</v>
@@ -18667,13 +18681,13 @@
         <v>84</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>539</v>
+        <v>84</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>540</v>
+        <v>84</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>84</v>
@@ -18691,7 +18705,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -18700,7 +18714,7 @@
         <v>95</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>726</v>
+        <v>84</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>107</v>
@@ -18715,38 +18729,38 @@
         <v>84</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>84</v>
+        <v>724</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>195</v>
+        <v>432</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>542</v>
+        <v>433</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR127" t="s" s="2">
-        <v>84</v>
+        <v>434</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>544</v>
+        <v>84</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>84</v>
@@ -18761,16 +18775,16 @@
         <v>245</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>545</v>
+        <v>726</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>546</v>
+        <v>727</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>547</v>
+        <v>728</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
@@ -18798,37 +18812,37 @@
         <v>153</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>728</v>
+        <v>542</v>
       </c>
       <c r="Z128" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI128" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>107</v>
@@ -18843,19 +18857,19 @@
         <v>84</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>551</v>
+        <v>84</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>552</v>
+        <v>195</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR128" t="s" s="2">
-        <v>554</v>
+        <v>84</v>
       </c>
     </row>
     <row r="129" hidden="true">
@@ -18867,7 +18881,7 @@
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>84</v>
+        <v>547</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -18886,19 +18900,19 @@
         <v>84</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>85</v>
+        <v>245</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>731</v>
+        <v>548</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>732</v>
+        <v>549</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>618</v>
+        <v>550</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>619</v>
+        <v>551</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -18923,13 +18937,13 @@
         <v>84</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>84</v>
+        <v>731</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>84</v>
+        <v>732</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>84</v>
@@ -18971,23 +18985,151 @@
         <v>84</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>84</v>
+        <v>554</v>
       </c>
       <c r="AO129" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AP129" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AQ129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR129" t="s" s="2">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="N130" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="AP129" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="AQ129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR129" t="s" s="2">
+      <c r="P130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AP130" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AQ130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR130" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR129">
+  <autoFilter ref="A1:AR130">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18997,7 +19139,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI128">
+  <conditionalFormatting sqref="A2:AI129">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/output/StructureDefinition-t-cabs-observation-beatmungsparameter.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-beatmungsparameter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T10:29:35+01:00</t>
+    <t>2025-12-09T09:55:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-beatmungsparameter.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-beatmungsparameter.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-observation-beatmungsparameter</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-beatmungsparameter</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T09:55:43+01:00</t>
+    <t>2026-02-19T13:21:58+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -716,7 +716,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-procedure-beatmung)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-procedure-beatmung)
 </t>
   </si>
   <si>
@@ -1056,7 +1056,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-patient)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-patient)
 </t>
   </si>
   <si>
@@ -1904,7 +1904,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-devicemetric-numericmetric)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-devicemetric-numericmetric)
 </t>
   </si>
   <si>
